--- a/Luban/Config/Datas/BulletData.xlsx
+++ b/Luban/Config/Datas/BulletData.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,7 +598,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>效果类型 0无/1减速/2持续伤害</t>
+          <t>效果类型 0无/1减速/2持续伤害/3范围伤害/4激光（命中时施加）</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -658,6 +658,182 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>M0 唯一子弹，直线追踪</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>爆炸弹</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bullet_Normal</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>AOE 塔专用：命中后对 aoeRadius 格内的其他敌人造成同等伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>穿透弹</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bullet_Normal</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>穿透：pierce=3 表示命中后还能再穿 3 个敌人（共可打 4 个）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>减速弹</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bullet_Normal</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>减速：effectValue=减速比例(0~1)。塔自身 effectValue&gt;0 时会覆盖此值（减速塔三级各不相同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>腐蚀弹</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bullet_Normal</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>持续伤害：effectValue=每秒伤害，持续时长由代码常数 DotDurationSec 决定</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/BulletData.xlsx
+++ b/Luban/Config/Datas/BulletData.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>AOE 塔专用：命中后对 aoeRadius 格内的其他敌人造成同等伤害</t>
+          <t>AOE 塔专用：弹体飞向发射瞬间锁定的落点，到达即引爆，对落点 aoeRadius 格内全部敌人造成同等伤害</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/BulletData.xlsx
+++ b/Luban/Config/Datas/BulletData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,30 +454,25 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>pierce</t>
+          <t>aoeRadius</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>aoeRadius</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>effectValue</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>effectValue</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t>scale</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
@@ -521,30 +516,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -588,30 +578,25 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>穿透数量 0=命中即消失</t>
+          <t>爆炸半径（格）0=单体</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>爆炸半径（格）0=单体</t>
+          <t>效果类型 0无/1减速/2持续伤害/3范围伤害（命中时施加）</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>效果类型 0无/1减速/2持续伤害/3范围伤害/4激光（命中时施加）</t>
+          <t>效果参数</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>效果参数</t>
+          <t>显示缩放</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
-        <is>
-          <t>显示缩放</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -650,12 +635,9 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>M0 唯一子弹，直线追踪</t>
         </is>
@@ -685,21 +667,18 @@
         <v>3000</v>
       </c>
       <c r="H5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
         <v>1.3</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>AOE 塔专用：弹体飞向发射瞬间锁定的落点，到达即引爆，对落点 aoeRadius 格内全部敌人造成同等伤害</t>
         </is>
@@ -707,11 +686,11 @@
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>穿透弹</t>
+          <t>减速弹</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -720,42 +699,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G6" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>穿透：pierce=3 表示命中后还能再穿 3 个敌人（共可打 4 个）</t>
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>减速：effectValue=减速比例(0~1)。塔自身 effectValue&gt;0 时会覆盖此值（减速塔三级各不相同）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>减速弹</t>
+          <t>腐蚀弹</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -776,62 +752,15 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>减速：effectValue=减速比例(0~1)。塔自身 effectValue&gt;0 时会覆盖此值（减速塔三级各不相同）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>腐蚀弹</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bullet_Normal</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>持续伤害：effectValue=每秒伤害，持续时长由代码常数 DotDurationSec 决定</t>
         </is>

--- a/Luban/Config/Datas/BulletData.xlsx
+++ b/Luban/Config/Datas/BulletData.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Luban/Config/Datas/BulletData.xlsx
+++ b/Luban/Config/Datas/BulletData.xlsx
@@ -667,7 +667,7 @@
         <v>3000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>

--- a/Luban/Config/Datas/BulletData.xlsx
+++ b/Luban/Config/Datas/BulletData.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,6 +763,88 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>持续伤害：effectValue=每秒伤害，持续时长由代码常数 DotDurationSec 决定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>爆炸弹II</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bullet_Normal</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>火力塔二级 AOE 0.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>爆炸弹III</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bullet_Normal</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>火力塔三级 AOE 1.05</t>
         </is>
       </c>
     </row>
